--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 09/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 09/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.79005</v>
+        <v>16.74809</v>
       </c>
       <c r="D2" t="n">
-        <v>16.05082</v>
+        <v>16.14972</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81693</v>
+        <v>16.57366</v>
       </c>
       <c r="F2" t="n">
-        <v>42.06761</v>
+        <v>42.44382</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05028</v>
+        <v>0.04935</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79895</v>
+        <v>1.79127</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.57147</v>
+        <v>16.61233</v>
       </c>
       <c r="D3" t="n">
-        <v>16.55985</v>
+        <v>16.27633</v>
       </c>
       <c r="E3" t="n">
-        <v>16.91803</v>
+        <v>16.51083</v>
       </c>
       <c r="F3" t="n">
-        <v>41.71768</v>
+        <v>41.85422</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04987</v>
+        <v>0.04956</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82318</v>
+        <v>1.80022</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.0744</v>
+        <v>16.95211</v>
       </c>
       <c r="D4" t="n">
-        <v>16.38899</v>
+        <v>16.35779</v>
       </c>
       <c r="E4" t="n">
-        <v>16.35302</v>
+        <v>16.53732</v>
       </c>
       <c r="F4" t="n">
-        <v>41.59912</v>
+        <v>42.13681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04931</v>
+        <v>0.05091</v>
       </c>
       <c r="H4" t="n">
-        <v>1.77484</v>
+        <v>1.81107</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.85776</v>
+        <v>16.63394</v>
       </c>
       <c r="D5" t="n">
-        <v>16.51577</v>
+        <v>16.20073</v>
       </c>
       <c r="E5" t="n">
-        <v>16.64078</v>
+        <v>16.36661</v>
       </c>
       <c r="F5" t="n">
-        <v>42.23086</v>
+        <v>42.60342</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05011</v>
+        <v>0.05069</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80151</v>
+        <v>1.76643</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.36495</v>
+        <v>16.69746</v>
       </c>
       <c r="D6" t="n">
-        <v>16.4485</v>
+        <v>16.2472</v>
       </c>
       <c r="E6" t="n">
-        <v>16.58061</v>
+        <v>16.45697</v>
       </c>
       <c r="F6" t="n">
-        <v>41.51116</v>
+        <v>41.97091</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04989</v>
+        <v>0.04979</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81464</v>
+        <v>1.77706</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.63166</v>
+        <v>16.61945</v>
       </c>
       <c r="D7" t="n">
-        <v>16.5884</v>
+        <v>16.30607</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56174</v>
+        <v>16.58336</v>
       </c>
       <c r="F7" t="n">
-        <v>41.73996</v>
+        <v>42.68069</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04975</v>
+        <v>0.04982</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79502</v>
+        <v>1.78675</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.49485</v>
+        <v>16.59439</v>
       </c>
       <c r="D8" t="n">
-        <v>16.49401</v>
+        <v>16.40059</v>
       </c>
       <c r="E8" t="n">
-        <v>16.64525</v>
+        <v>16.55113</v>
       </c>
       <c r="F8" t="n">
-        <v>41.9648</v>
+        <v>41.66664</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04918</v>
+        <v>0.04954</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81111</v>
+        <v>1.82409</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.64233</v>
+        <v>16.47194</v>
       </c>
       <c r="D9" t="n">
-        <v>16.17263</v>
+        <v>16.3973</v>
       </c>
       <c r="E9" t="n">
-        <v>16.73468</v>
+        <v>16.41912</v>
       </c>
       <c r="F9" t="n">
-        <v>41.17338</v>
+        <v>41.38961</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04965</v>
+        <v>0.05071</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82651</v>
+        <v>1.79451</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.94224</v>
+        <v>16.68741</v>
       </c>
       <c r="D10" t="n">
-        <v>16.42687</v>
+        <v>16.5508</v>
       </c>
       <c r="E10" t="n">
-        <v>16.44256</v>
+        <v>16.60549</v>
       </c>
       <c r="F10" t="n">
-        <v>41.1242</v>
+        <v>42.558</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04996</v>
+        <v>0.04992</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84865</v>
+        <v>1.79926</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59857</v>
+        <v>0.60572</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09786</v>
+        <v>1.0987</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.61668</v>
+        <v>0.59783</v>
       </c>
       <c r="D13" t="n">
-        <v>1.07875</v>
+        <v>1.12158</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.59738</v>
+        <v>0.58955</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09996</v>
+        <v>1.10994</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.58107</v>
+        <v>0.58814</v>
       </c>
       <c r="D15" t="n">
-        <v>1.12075</v>
+        <v>1.08945</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5982499999999999</v>
+        <v>0.59272</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10826</v>
+        <v>1.12306</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.61022</v>
+        <v>0.61066</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09248</v>
+        <v>1.08586</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.60914</v>
+        <v>0.59067</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08918</v>
+        <v>1.07292</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60722</v>
+        <v>0.60141</v>
       </c>
       <c r="D19" t="n">
-        <v>1.06638</v>
+        <v>1.09589</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60823</v>
+        <v>0.59697</v>
       </c>
       <c r="D20" t="n">
-        <v>1.07376</v>
+        <v>1.109</v>
       </c>
     </row>
   </sheetData>
